--- a/data-raw/metadata/lower_feather_release_metadata.xlsx
+++ b/data-raw/metadata/lower_feather_release_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Badhia\Documents\git\jpe-lower-feather-edi\data-raw\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D3F143-1A14-43B3-8317-2C4AC69396BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC80CCF-46A0-4E71-B1A3-63F5EC87F9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5560" yWindow="2350" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="680" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attribute" sheetId="1" r:id="rId1"/>
@@ -928,7 +928,7 @@
         <v>44593.500127314815</v>
       </c>
       <c r="M10" s="14">
-        <v>45779.583460648151</v>
+        <v>46031.477905092594</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
